--- a/output/pdf_financials_xlsx/LXE.xlsx
+++ b/output/pdf_financials_xlsx/LXE.xlsx
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.792141</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.171491</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.117611</v>
       </c>
     </row>
     <row r="93">
@@ -3896,7 +3896,11 @@
           <t>Share-based payment reserves (note 8) 3,156,465</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4528,7 +4532,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>1.792141</v>
       </c>

--- a/output/pdf_financials_xlsx/LXE.xlsx
+++ b/output/pdf_financials_xlsx/LXE.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004841</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.013296</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00115</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001036</v>
       </c>
     </row>
     <row r="13">
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.8079229999999999</v>
+        <v>-0.812764</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.64054</v>
+        <v>-0.653836</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.176654</v>
+        <v>-2.177804</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.260284</v>
+        <v>-1.26132</v>
       </c>
     </row>
     <row r="28">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.805417</v>
+        <v>-0.810258</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.639103</v>
+        <v>-0.652399</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.157128</v>
+        <v>-2.158278</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.258655</v>
+        <v>-1.259691</v>
       </c>
     </row>
     <row r="30">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">

--- a/output/pdf_financials_xlsx/LXE.xlsx
+++ b/output/pdf_financials_xlsx/LXE.xlsx
@@ -550,10 +550,10 @@
         <v>0.271135</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.539368</v>
+        <v>0.853085</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.67765</v>
+        <v>1.096265</v>
       </c>
     </row>
     <row r="8">
@@ -607,10 +607,10 @@
         <v>0.38626</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.594739</v>
+        <v>0.908456</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.726123</v>
+        <v>1.144738</v>
       </c>
     </row>
     <row r="11">
@@ -6152,7 +6152,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>3.09975</v>
       </c>
@@ -6804,7 +6808,11 @@
           <t>Salaries, benefits, and directors’ fees (note 10)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
